--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/131.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/131.xlsx
@@ -426,13 +426,13 @@
         <v>-3.504073925977822</v>
       </c>
       <c r="E2">
-        <v>-13.01655266640112</v>
+        <v>-13.14784218483149</v>
       </c>
       <c r="F2">
-        <v>0.5194218341061027</v>
+        <v>1.560976214955283</v>
       </c>
       <c r="G2">
-        <v>-7.405171766368314</v>
+        <v>-7.918630758418196</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.304643052789163</v>
       </c>
       <c r="E3">
-        <v>-14.96707510488092</v>
+        <v>-14.75178692208227</v>
       </c>
       <c r="F3">
-        <v>0.8902454721737181</v>
+        <v>1.849097308262202</v>
       </c>
       <c r="G3">
-        <v>-6.589562593494689</v>
+        <v>-7.257226796763824</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-3.084127747170035</v>
       </c>
       <c r="E4">
-        <v>-15.22652949467639</v>
+        <v>-14.10101350786198</v>
       </c>
       <c r="F4">
-        <v>0.8604143052641023</v>
+        <v>1.597566859871743</v>
       </c>
       <c r="G4">
-        <v>-7.157337706207394</v>
+        <v>-6.900998854556087</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.849545409948699</v>
       </c>
       <c r="E5">
-        <v>-15.54719979610754</v>
+        <v>-15.15654645736185</v>
       </c>
       <c r="F5">
-        <v>0.9463855877962463</v>
+        <v>2.316661005098355</v>
       </c>
       <c r="G5">
-        <v>-6.743930021445365</v>
+        <v>-6.790701408824189</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.582569414488024</v>
       </c>
       <c r="E6">
-        <v>-15.69839195780163</v>
+        <v>-17.70063862639705</v>
       </c>
       <c r="F6">
-        <v>1.191254305533391</v>
+        <v>1.914755365342896</v>
       </c>
       <c r="G6">
-        <v>-6.497645296596825</v>
+        <v>-6.630252508717871</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.275990938424923</v>
       </c>
       <c r="E7">
-        <v>-17.60000234852459</v>
+        <v>-17.66313833313953</v>
       </c>
       <c r="F7">
-        <v>1.143823644783897</v>
+        <v>2.369038675977368</v>
       </c>
       <c r="G7">
-        <v>-6.000626473694963</v>
+        <v>-5.745999174087459</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.920498021460743</v>
       </c>
       <c r="E8">
-        <v>-18.43369894181071</v>
+        <v>-16.88046405649783</v>
       </c>
       <c r="F8">
-        <v>0.904834678871823</v>
+        <v>1.840300046444471</v>
       </c>
       <c r="G8">
-        <v>-5.3312738922008</v>
+        <v>-4.766243221740151</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-1.516067556806198</v>
       </c>
       <c r="E9">
-        <v>-17.55157031901256</v>
+        <v>-17.47565498074797</v>
       </c>
       <c r="F9">
-        <v>1.103331389400252</v>
+        <v>2.202376124738524</v>
       </c>
       <c r="G9">
-        <v>-5.467578983689212</v>
+        <v>-3.88248315839509</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-1.069775957895314</v>
       </c>
       <c r="E10">
-        <v>-18.95662447784645</v>
+        <v>-18.23720392614389</v>
       </c>
       <c r="F10">
-        <v>1.142382285503026</v>
+        <v>2.079832421372782</v>
       </c>
       <c r="G10">
-        <v>-5.045196409970219</v>
+        <v>-3.508527244824556</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-0.5981654337453322</v>
       </c>
       <c r="E11">
-        <v>-20.86876357063724</v>
+        <v>-20.18047627773742</v>
       </c>
       <c r="F11">
-        <v>1.68907826359381</v>
+        <v>2.238701692086088</v>
       </c>
       <c r="G11">
-        <v>-4.167150348225941</v>
+        <v>-3.627988280609157</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-0.1228015379446745</v>
       </c>
       <c r="E12">
-        <v>-21.57175029016596</v>
+        <v>-20.72329087161484</v>
       </c>
       <c r="F12">
-        <v>1.531087062327472</v>
+        <v>2.537651204082402</v>
       </c>
       <c r="G12">
-        <v>-3.759850619983867</v>
+        <v>-3.545476243588361</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.3372264403177112</v>
       </c>
       <c r="E13">
-        <v>-22.20167913852894</v>
+        <v>-21.44458621155657</v>
       </c>
       <c r="F13">
-        <v>1.239750246762886</v>
+        <v>2.393770413155349</v>
       </c>
       <c r="G13">
-        <v>-2.202910984501246</v>
+        <v>-3.159920178448221</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>0.7685658488227824</v>
       </c>
       <c r="E14">
-        <v>-22.39069311513509</v>
+        <v>-22.2358374179688</v>
       </c>
       <c r="F14">
-        <v>1.766141283076248</v>
+        <v>2.029958076785029</v>
       </c>
       <c r="G14">
-        <v>-1.953418341025151</v>
+        <v>-1.7731392731386</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.167510450798088</v>
       </c>
       <c r="E15">
-        <v>-23.29592601232038</v>
+        <v>-24.49376172903728</v>
       </c>
       <c r="F15">
-        <v>1.500084583910297</v>
+        <v>2.561617529780197</v>
       </c>
       <c r="G15">
-        <v>-1.120332798249714</v>
+        <v>-0.2185898515353319</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.538478112382921</v>
       </c>
       <c r="E16">
-        <v>-23.91553446841988</v>
+        <v>-23.33533732160914</v>
       </c>
       <c r="F16">
-        <v>1.921708681321995</v>
+        <v>2.569545005824988</v>
       </c>
       <c r="G16">
-        <v>-1.103548332365609</v>
+        <v>-1.166071295420285</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>1.887303699324506</v>
       </c>
       <c r="E17">
-        <v>-24.61623883704874</v>
+        <v>-24.6930281707968</v>
       </c>
       <c r="F17">
-        <v>1.808331691635633</v>
+        <v>2.794778102646173</v>
       </c>
       <c r="G17">
-        <v>0.3738322727172471</v>
+        <v>-0.3660382393089313</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.217173207146389</v>
       </c>
       <c r="E18">
-        <v>-24.94326258751265</v>
+        <v>-26.04745851869895</v>
       </c>
       <c r="F18">
-        <v>2.057203080663105</v>
+        <v>3.250280770097566</v>
       </c>
       <c r="G18">
-        <v>0.02232516844851097</v>
+        <v>-0.2594949522185667</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.523858522976443</v>
       </c>
       <c r="E19">
-        <v>-25.45186908873613</v>
+        <v>-26.05030692884977</v>
       </c>
       <c r="F19">
-        <v>2.336631286445045</v>
+        <v>3.776776180703681</v>
       </c>
       <c r="G19">
-        <v>0.9955163089914441</v>
+        <v>0.08128598450293081</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.795745829175305</v>
       </c>
       <c r="E20">
-        <v>-27.02461264007406</v>
+        <v>-26.11583847621477</v>
       </c>
       <c r="F20">
-        <v>2.095773523672256</v>
+        <v>4.069569266162389</v>
       </c>
       <c r="G20">
-        <v>0.7329006629976785</v>
+        <v>0.909356050786372</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.016958887138137</v>
       </c>
       <c r="E21">
-        <v>-28.30676854281378</v>
+        <v>-26.68473255190236</v>
       </c>
       <c r="F21">
-        <v>2.18673986164328</v>
+        <v>3.845555526158124</v>
       </c>
       <c r="G21">
-        <v>1.121727547130619</v>
+        <v>0.9236046387873953</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.170860876068467</v>
       </c>
       <c r="E22">
-        <v>-27.80840092132164</v>
+        <v>-27.46092205376508</v>
       </c>
       <c r="F22">
-        <v>2.460697529097133</v>
+        <v>3.892225745631848</v>
       </c>
       <c r="G22">
-        <v>1.794592617441948</v>
+        <v>0.9140801992709121</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.246286939318187</v>
       </c>
       <c r="E23">
-        <v>-27.8472235289894</v>
+        <v>-28.63890494043235</v>
       </c>
       <c r="F23">
-        <v>2.663798305650321</v>
+        <v>4.038119469347703</v>
       </c>
       <c r="G23">
-        <v>1.099050310186611</v>
+        <v>1.024086316995354</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.238205304887928</v>
       </c>
       <c r="E24">
-        <v>-28.29242686563149</v>
+        <v>-27.7346366082107</v>
       </c>
       <c r="F24">
-        <v>2.999316925010622</v>
+        <v>4.309833917874774</v>
       </c>
       <c r="G24">
-        <v>2.048968315588468</v>
+        <v>0.2261455256648202</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>3.152768271886867</v>
       </c>
       <c r="E25">
-        <v>-28.05131732404109</v>
+        <v>-29.11090325777783</v>
       </c>
       <c r="F25">
-        <v>2.966245184821255</v>
+        <v>4.404113725456997</v>
       </c>
       <c r="G25">
-        <v>1.651520770871265</v>
+        <v>1.025983259589357</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.000694606474306</v>
       </c>
       <c r="E26">
-        <v>-28.75593882268659</v>
+        <v>-28.34982527367871</v>
       </c>
       <c r="F26">
-        <v>2.858004073032248</v>
+        <v>4.290062444704756</v>
       </c>
       <c r="G26">
-        <v>1.150393560955168</v>
+        <v>0.6030279614920699</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.800762336535478</v>
       </c>
       <c r="E27">
-        <v>-29.38664656857888</v>
+        <v>-27.75021455879708</v>
       </c>
       <c r="F27">
-        <v>2.643649096944626</v>
+        <v>3.971972675499357</v>
       </c>
       <c r="G27">
-        <v>1.696948076761145</v>
+        <v>1.183396389436162</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.570127430513031</v>
       </c>
       <c r="E28">
-        <v>-28.9624055381183</v>
+        <v>-28.64479195664233</v>
       </c>
       <c r="F28">
-        <v>2.935161526398606</v>
+        <v>4.361432923395156</v>
       </c>
       <c r="G28">
-        <v>0.6867913847267094</v>
+        <v>1.62106706245551</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.327301543045936</v>
       </c>
       <c r="E29">
-        <v>-28.60985930814716</v>
+        <v>-28.94565018428992</v>
       </c>
       <c r="F29">
-        <v>3.047489802953024</v>
+        <v>4.344835754112665</v>
       </c>
       <c r="G29">
-        <v>1.756878882658571</v>
+        <v>0.7442823185616929</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.085023377143813</v>
       </c>
       <c r="E30">
-        <v>-27.84495476351156</v>
+        <v>-27.72905299975924</v>
       </c>
       <c r="F30">
-        <v>3.003276521196003</v>
+        <v>4.355422289520442</v>
       </c>
       <c r="G30">
-        <v>0.5256704438759201</v>
+        <v>0.8530072551624373</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.852606747027493</v>
       </c>
       <c r="E31">
-        <v>-27.56072056394612</v>
+        <v>-27.19611047921854</v>
       </c>
       <c r="F31">
-        <v>2.871990228261116</v>
+        <v>4.106270912310824</v>
       </c>
       <c r="G31">
-        <v>1.43151184596792</v>
+        <v>0.3200491498862474</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.634373999155269</v>
       </c>
       <c r="E32">
-        <v>-26.99631420600012</v>
+        <v>-25.90493838472954</v>
       </c>
       <c r="F32">
-        <v>2.960792870576028</v>
+        <v>3.954232359201002</v>
       </c>
       <c r="G32">
-        <v>0.3747989520147142</v>
+        <v>0.9111470559231178</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.428791574314646</v>
       </c>
       <c r="E33">
-        <v>-27.59059490697472</v>
+        <v>-26.78869272969645</v>
       </c>
       <c r="F33">
-        <v>3.139705318967471</v>
+        <v>4.401081900762751</v>
       </c>
       <c r="G33">
-        <v>1.077962135101454</v>
+        <v>0.953631286828585</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.231560713614832</v>
       </c>
       <c r="E34">
-        <v>-26.16663436915881</v>
+        <v>-25.49753422062948</v>
       </c>
       <c r="F34">
-        <v>2.934773850454095</v>
+        <v>4.209208815987107</v>
       </c>
       <c r="G34">
-        <v>0.2201302644199644</v>
+        <v>0.3957215998229082</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.03277603065165</v>
       </c>
       <c r="E35">
-        <v>-25.76343715741187</v>
+        <v>-24.36905208334005</v>
       </c>
       <c r="F35">
-        <v>2.864382502033805</v>
+        <v>4.080480521592063</v>
       </c>
       <c r="G35">
-        <v>-0.1827035378896322</v>
+        <v>-0.1169428612975493</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.8254031598754997</v>
       </c>
       <c r="E36">
-        <v>-25.11274978419773</v>
+        <v>-24.69759740107054</v>
       </c>
       <c r="F36">
-        <v>2.918652164060811</v>
+        <v>3.960627355550614</v>
       </c>
       <c r="G36">
-        <v>0.3064295655376857</v>
+        <v>-0.06691720765362241</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.6013590788065923</v>
       </c>
       <c r="E37">
-        <v>-24.69566374266927</v>
+        <v>-24.87524943639145</v>
       </c>
       <c r="F37">
-        <v>3.145651340184766</v>
+        <v>4.216374194021323</v>
       </c>
       <c r="G37">
-        <v>0.3095050623436686</v>
+        <v>-0.3462113820742361</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.358390216796722</v>
       </c>
       <c r="E38">
-        <v>-23.75328377319906</v>
+        <v>-24.38741957391516</v>
       </c>
       <c r="F38">
-        <v>3.206745092876035</v>
+        <v>4.338743940232477</v>
       </c>
       <c r="G38">
-        <v>-0.1523888723865259</v>
+        <v>0.1864024264658695</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>0.09730837794942539</v>
       </c>
       <c r="E39">
-        <v>-23.16384401093866</v>
+        <v>-23.93250266052662</v>
       </c>
       <c r="F39">
-        <v>2.865404707408859</v>
+        <v>4.409690294812643</v>
       </c>
       <c r="G39">
-        <v>-0.7203228912851158</v>
+        <v>0.006126669124857054</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.1758814637671578</v>
       </c>
       <c r="E40">
-        <v>-23.43516300263422</v>
+        <v>-22.89977057765537</v>
       </c>
       <c r="F40">
-        <v>3.297472861035053</v>
+        <v>3.840721173995386</v>
       </c>
       <c r="G40">
-        <v>-0.4494110181699368</v>
+        <v>-0.4446603853210827</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.4519061643056818</v>
       </c>
       <c r="E41">
-        <v>-21.86709283647222</v>
+        <v>-22.02659021949637</v>
       </c>
       <c r="F41">
-        <v>3.623925827539116</v>
+        <v>4.20483337936552</v>
       </c>
       <c r="G41">
-        <v>-0.5765988672431965</v>
+        <v>-0.7119604532529169</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-0.7188281360941545</v>
       </c>
       <c r="E42">
-        <v>-21.60792374053923</v>
+        <v>-21.30023657408807</v>
       </c>
       <c r="F42">
-        <v>3.520487589951542</v>
+        <v>4.003906238877278</v>
       </c>
       <c r="G42">
-        <v>-0.8216851746065211</v>
+        <v>-0.3195813537563387</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-0.9650321532404611</v>
       </c>
       <c r="E43">
-        <v>-20.6394371184148</v>
+        <v>-20.77610193549229</v>
       </c>
       <c r="F43">
-        <v>3.834288072745245</v>
+        <v>4.131797882195493</v>
       </c>
       <c r="G43">
-        <v>-1.405191999721843</v>
+        <v>-0.636274761134099</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.181099430087976</v>
       </c>
       <c r="E44">
-        <v>-19.48215388643659</v>
+        <v>-21.38596058705327</v>
       </c>
       <c r="F44">
-        <v>3.536090718350673</v>
+        <v>4.444899222901234</v>
       </c>
       <c r="G44">
-        <v>-1.076666702586727</v>
+        <v>0.03076374902811323</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.36151132020392</v>
       </c>
       <c r="E45">
-        <v>-19.33462526021471</v>
+        <v>-20.06428469164861</v>
       </c>
       <c r="F45">
-        <v>3.884881440238628</v>
+        <v>4.117014837525133</v>
       </c>
       <c r="G45">
-        <v>-1.041320007863929</v>
+        <v>-0.7743609261226395</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.503816787587767</v>
       </c>
       <c r="E46">
-        <v>-19.31936430280886</v>
+        <v>-18.85559422273532</v>
       </c>
       <c r="F46">
-        <v>3.815439400861945</v>
+        <v>4.319664982211199</v>
       </c>
       <c r="G46">
-        <v>-2.055005741443227</v>
+        <v>-0.7478103508976846</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.610015656107026</v>
       </c>
       <c r="E47">
-        <v>-18.46074298858452</v>
+        <v>-18.08269239300218</v>
       </c>
       <c r="F47">
-        <v>3.566887761651953</v>
+        <v>4.480232406100243</v>
       </c>
       <c r="G47">
-        <v>-1.40084194288324</v>
+        <v>-0.6122699954288436</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.683640886951151</v>
       </c>
       <c r="E48">
-        <v>-17.67455914458688</v>
+        <v>-18.56500657413712</v>
       </c>
       <c r="F48">
-        <v>3.421292250201107</v>
+        <v>4.863642258485995</v>
       </c>
       <c r="G48">
-        <v>-1.54606233350891</v>
+        <v>-1.624565299881648</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.73297635939309</v>
       </c>
       <c r="E49">
-        <v>-17.28056379202352</v>
+        <v>-17.38995361015281</v>
       </c>
       <c r="F49">
-        <v>3.760265161631081</v>
+        <v>4.607535908562472</v>
       </c>
       <c r="G49">
-        <v>-2.129777722993206</v>
+        <v>-1.295996965654522</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-1.764892546902598</v>
       </c>
       <c r="E50">
-        <v>-16.59849862241024</v>
+        <v>-16.22858569461968</v>
       </c>
       <c r="F50">
-        <v>3.900683376814431</v>
+        <v>4.560782852348468</v>
       </c>
       <c r="G50">
-        <v>-2.012024928706869</v>
+        <v>-2.022092297691793</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-1.789178999848863</v>
       </c>
       <c r="E51">
-        <v>-17.06254946787225</v>
+        <v>-15.49527178466159</v>
       </c>
       <c r="F51">
-        <v>3.832303304448137</v>
+        <v>4.673005097875328</v>
       </c>
       <c r="G51">
-        <v>-1.480622779834137</v>
+        <v>-1.682539573365365</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-1.812148622913081</v>
       </c>
       <c r="E52">
-        <v>-15.38055648109928</v>
+        <v>-15.86987621152409</v>
       </c>
       <c r="F52">
-        <v>4.33659349845481</v>
+        <v>4.374375335696495</v>
       </c>
       <c r="G52">
-        <v>-2.665384264700813</v>
+        <v>-2.06552996571257</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-1.839820912012072</v>
       </c>
       <c r="E53">
-        <v>-15.06037072638695</v>
+        <v>-15.59171469560294</v>
       </c>
       <c r="F53">
-        <v>3.600883959862845</v>
+        <v>4.441940294538433</v>
       </c>
       <c r="G53">
-        <v>-1.847550405224798</v>
+        <v>-1.331201306919132</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-1.875826242918708</v>
       </c>
       <c r="E54">
-        <v>-14.87574031262022</v>
+        <v>-15.11889219598807</v>
       </c>
       <c r="F54">
-        <v>3.777163856648191</v>
+        <v>4.680503479605469</v>
       </c>
       <c r="G54">
-        <v>-2.840310180450363</v>
+        <v>-2.378823442821499</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-1.921469784421571</v>
       </c>
       <c r="E55">
-        <v>-14.24212981488901</v>
+        <v>-13.89163951211734</v>
       </c>
       <c r="F55">
-        <v>3.670672256813898</v>
+        <v>4.627145021721542</v>
       </c>
       <c r="G55">
-        <v>-3.297029732502677</v>
+        <v>-2.1271723236538</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-1.979606463334368</v>
       </c>
       <c r="E56">
-        <v>-13.17182498317612</v>
+        <v>-14.19598919322485</v>
       </c>
       <c r="F56">
-        <v>3.642254284693458</v>
+        <v>4.354148260454936</v>
       </c>
       <c r="G56">
-        <v>-3.128595796555637</v>
+        <v>-2.448321725327419</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-2.048837670512155</v>
       </c>
       <c r="E57">
-        <v>-12.88395894745653</v>
+        <v>-13.81394448356774</v>
       </c>
       <c r="F57">
-        <v>3.762372528303803</v>
+        <v>4.359358691418545</v>
       </c>
       <c r="G57">
-        <v>-3.233963839979561</v>
+        <v>-2.39022165111321</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-2.132009202990729</v>
       </c>
       <c r="E58">
-        <v>-11.77209630977525</v>
+        <v>-12.88014144386806</v>
       </c>
       <c r="F58">
-        <v>3.693608093462611</v>
+        <v>4.536114071093098</v>
       </c>
       <c r="G58">
-        <v>-3.99840191045267</v>
+        <v>-2.114261196050642</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-2.224139491290947</v>
       </c>
       <c r="E59">
-        <v>-11.44582428599661</v>
+        <v>-13.29177067421728</v>
       </c>
       <c r="F59">
-        <v>3.675713700827336</v>
+        <v>4.463128275967239</v>
       </c>
       <c r="G59">
-        <v>-3.839071974738627</v>
+        <v>-4.578975592220198</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-2.325882790478323</v>
       </c>
       <c r="E60">
-        <v>-11.59938936807072</v>
+        <v>-12.08518141724355</v>
       </c>
       <c r="F60">
-        <v>3.504915939513717</v>
+        <v>4.318210369051883</v>
       </c>
       <c r="G60">
-        <v>-4.668933046158814</v>
+        <v>-3.663745482978825</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-2.430101697167318</v>
       </c>
       <c r="E61">
-        <v>-11.83787239473666</v>
+        <v>-12.16922989482592</v>
       </c>
       <c r="F61">
-        <v>3.481198124036761</v>
+        <v>4.467883104859308</v>
       </c>
       <c r="G61">
-        <v>-4.572589549874944</v>
+        <v>-4.5516205544292</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-2.534368732610209</v>
       </c>
       <c r="E62">
-        <v>-11.59313101699212</v>
+        <v>-11.42902364742815</v>
       </c>
       <c r="F62">
-        <v>3.500696235963856</v>
+        <v>4.335538158383643</v>
       </c>
       <c r="G62">
-        <v>-5.127158896431496</v>
+        <v>-5.232351480941838</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-2.630777023202555</v>
       </c>
       <c r="E63">
-        <v>-10.99380106749897</v>
+        <v>-11.5543944503305</v>
       </c>
       <c r="F63">
-        <v>3.297346949189828</v>
+        <v>4.002025844872922</v>
       </c>
       <c r="G63">
-        <v>-4.793667780987474</v>
+        <v>-4.260060808785586</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-2.713495763140711</v>
       </c>
       <c r="E64">
-        <v>-10.25439183152655</v>
+        <v>-10.49292919988059</v>
       </c>
       <c r="F64">
-        <v>3.21901155737669</v>
+        <v>4.172894845783182</v>
       </c>
       <c r="G64">
-        <v>-4.860610322337076</v>
+        <v>-5.68489643506913</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-2.77558022045437</v>
       </c>
       <c r="E65">
-        <v>-10.68685204231105</v>
+        <v>-11.48105128530228</v>
       </c>
       <c r="F65">
-        <v>3.355334324120599</v>
+        <v>3.961419274787691</v>
       </c>
       <c r="G65">
-        <v>-5.448351335197126</v>
+        <v>-5.138954370187919</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-2.809950626463112</v>
       </c>
       <c r="E66">
-        <v>-9.670499449925551</v>
+        <v>-11.31225241666636</v>
       </c>
       <c r="F66">
-        <v>3.120763869935057</v>
+        <v>4.078053405101861</v>
       </c>
       <c r="G66">
-        <v>-4.787539961194282</v>
+        <v>-4.411220318108709</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-2.812155116173472</v>
       </c>
       <c r="E67">
-        <v>-10.84857290607298</v>
+        <v>-10.96755403215051</v>
       </c>
       <c r="F67">
-        <v>2.91216273382728</v>
+        <v>4.176183464372296</v>
       </c>
       <c r="G67">
-        <v>-5.24683180713061</v>
+        <v>-5.214610267396884</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-2.776338931391943</v>
       </c>
       <c r="E68">
-        <v>-9.858141298907379</v>
+        <v>-11.47567145818116</v>
       </c>
       <c r="F68">
-        <v>2.779766428572641</v>
+        <v>3.746068601081904</v>
       </c>
       <c r="G68">
-        <v>-5.757963485666385</v>
+        <v>-5.53191281515387</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-2.701611740440404</v>
       </c>
       <c r="E69">
-        <v>-9.862701472233104</v>
+        <v>-10.61959967482314</v>
       </c>
       <c r="F69">
-        <v>2.835535435598715</v>
+        <v>3.87678332050886</v>
       </c>
       <c r="G69">
-        <v>-5.983123619428836</v>
+        <v>-5.202857830732471</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-2.58446729134652</v>
       </c>
       <c r="E70">
-        <v>-10.54081328403769</v>
+        <v>-10.60447910011153</v>
       </c>
       <c r="F70">
-        <v>2.493230830474681</v>
+        <v>4.156373886301749</v>
       </c>
       <c r="G70">
-        <v>-5.509391173850208</v>
+        <v>-4.48979611648331</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-2.42763047097729</v>
       </c>
       <c r="E71">
-        <v>-9.562785167179104</v>
+        <v>-9.639171466740487</v>
       </c>
       <c r="F71">
-        <v>2.861025957317661</v>
+        <v>3.555274050664704</v>
       </c>
       <c r="G71">
-        <v>-5.135521334463695</v>
+        <v>-5.469525584466304</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-2.232527204809824</v>
       </c>
       <c r="E72">
-        <v>-9.638428797003229</v>
+        <v>-11.31434910013191</v>
       </c>
       <c r="F72">
-        <v>2.63827961943968</v>
+        <v>3.360074242399418</v>
       </c>
       <c r="G72">
-        <v>-5.612398798304631</v>
+        <v>-5.544416745655697</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-2.00530386065646</v>
       </c>
       <c r="E73">
-        <v>-10.48962341385499</v>
+        <v>-10.33348615854452</v>
       </c>
       <c r="F73">
-        <v>2.489718552686811</v>
+        <v>3.562391383389558</v>
       </c>
       <c r="G73">
-        <v>-5.490507822094205</v>
+        <v>-5.338202864014495</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-1.751423427674607</v>
       </c>
       <c r="E74">
-        <v>-9.097792399123495</v>
+        <v>-11.27963381838911</v>
       </c>
       <c r="F74">
-        <v>2.583617311263746</v>
+        <v>3.45867978455906</v>
       </c>
       <c r="G74">
-        <v>-4.281251610782461</v>
+        <v>-4.219970102305012</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-1.478882527044754</v>
       </c>
       <c r="E75">
-        <v>-10.61302885903801</v>
+        <v>-10.47193519438103</v>
       </c>
       <c r="F75">
-        <v>2.601341060214044</v>
+        <v>3.269936271831192</v>
       </c>
       <c r="G75">
-        <v>-4.522961161695729</v>
+        <v>-5.080245155594484</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-1.195407001168136</v>
       </c>
       <c r="E76">
-        <v>-10.24209249612172</v>
+        <v>-11.10647855775782</v>
       </c>
       <c r="F76">
-        <v>2.061331663798657</v>
+        <v>2.916417228808058</v>
       </c>
       <c r="G76">
-        <v>-4.065394109985363</v>
+        <v>-4.278977265996982</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-0.9085586667988448</v>
       </c>
       <c r="E77">
-        <v>-11.37659297536734</v>
+        <v>-10.99671740475991</v>
       </c>
       <c r="F77">
-        <v>2.391621628112488</v>
+        <v>2.966952610583245</v>
       </c>
       <c r="G77">
-        <v>-4.086445869069587</v>
+        <v>-4.755037025089718</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-0.6253864867140447</v>
       </c>
       <c r="E78">
-        <v>-10.1593119912615</v>
+        <v>-12.38551887038027</v>
       </c>
       <c r="F78">
-        <v>1.896327504100219</v>
+        <v>3.101940049073841</v>
       </c>
       <c r="G78">
-        <v>-3.47612031454063</v>
+        <v>-3.167110683359518</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-0.350342710694685</v>
       </c>
       <c r="E79">
-        <v>-11.68707873875525</v>
+        <v>-12.72423514073199</v>
       </c>
       <c r="F79">
-        <v>1.709525684564513</v>
+        <v>2.822586396358153</v>
       </c>
       <c r="G79">
-        <v>-3.916081885073153</v>
+        <v>-3.482748026710251</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-0.08697429493415015</v>
       </c>
       <c r="E80">
-        <v>-12.31649586955536</v>
+        <v>-12.25461427224054</v>
       </c>
       <c r="F80">
-        <v>1.902260271439069</v>
+        <v>3.115550125501837</v>
       </c>
       <c r="G80">
-        <v>-3.314082352575463</v>
+        <v>-2.989572747179483</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>0.1647116829964259</v>
       </c>
       <c r="E81">
-        <v>-12.74367587964692</v>
+        <v>-13.71243421021181</v>
       </c>
       <c r="F81">
-        <v>1.793144403672706</v>
+        <v>2.851572628516913</v>
       </c>
       <c r="G81">
-        <v>-3.21397807655898</v>
+        <v>-2.275521179814081</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>0.4045308452595588</v>
       </c>
       <c r="E82">
-        <v>-13.41285754070838</v>
+        <v>-14.47640136072782</v>
       </c>
       <c r="F82">
-        <v>1.879505018884166</v>
+        <v>3.115485512844419</v>
       </c>
       <c r="G82">
-        <v>-2.390466631483116</v>
+        <v>-3.061073909736662</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>0.6327073611036924</v>
       </c>
       <c r="E83">
-        <v>-13.64628679038176</v>
+        <v>-14.58598137476542</v>
       </c>
       <c r="F83">
-        <v>2.167367661561411</v>
+        <v>2.971743887641038</v>
       </c>
       <c r="G83">
-        <v>-2.077358544924386</v>
+        <v>-2.577423069722377</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>0.8511661155782494</v>
       </c>
       <c r="E84">
-        <v>-14.40841085197665</v>
+        <v>-15.62584127572475</v>
       </c>
       <c r="F84">
-        <v>1.962426252639202</v>
+        <v>2.851471567693772</v>
       </c>
       <c r="G84">
-        <v>-2.656303438286592</v>
+        <v>-2.910877769165467</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>1.061578833991175</v>
       </c>
       <c r="E85">
-        <v>-16.22819171738101</v>
+        <v>-15.75339027462479</v>
       </c>
       <c r="F85">
-        <v>1.564470268660292</v>
+        <v>2.728089556516396</v>
       </c>
       <c r="G85">
-        <v>-1.955907871270683</v>
+        <v>-2.169295705095486</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>1.266633429974021</v>
       </c>
       <c r="E86">
-        <v>-16.85454307127793</v>
+        <v>-17.9720663014688</v>
       </c>
       <c r="F86">
-        <v>1.597961162755476</v>
+        <v>2.816323938792989</v>
       </c>
       <c r="G86">
-        <v>-1.338411675103664</v>
+        <v>-2.11717778667074</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>1.468423771641633</v>
       </c>
       <c r="E87">
-        <v>-17.74721398156594</v>
+        <v>-17.2460704055071</v>
       </c>
       <c r="F87">
-        <v>1.74963357747326</v>
+        <v>3.069809334254054</v>
       </c>
       <c r="G87">
-        <v>-1.18203805655619</v>
+        <v>-1.803043430994836</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.667946891888132</v>
       </c>
       <c r="E88">
-        <v>-19.01959743739711</v>
+        <v>-19.96601227720815</v>
       </c>
       <c r="F88">
-        <v>1.587591659607231</v>
+        <v>2.544975628657955</v>
       </c>
       <c r="G88">
-        <v>-0.9206009647744049</v>
+        <v>-1.262765709531318</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.865881242287483</v>
       </c>
       <c r="E89">
-        <v>-21.14439819806211</v>
+        <v>-21.22538542721529</v>
       </c>
       <c r="F89">
-        <v>1.270727874157976</v>
+        <v>2.206430154807824</v>
       </c>
       <c r="G89">
-        <v>-0.9442316388337226</v>
+        <v>-1.49968490104926</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>2.05980368963506</v>
       </c>
       <c r="E90">
-        <v>-21.7921647055413</v>
+        <v>-22.13033303053809</v>
       </c>
       <c r="F90">
-        <v>1.167392354128349</v>
+        <v>2.397887399147263</v>
       </c>
       <c r="G90">
-        <v>-1.184434891526622</v>
+        <v>-1.063179540059736</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.247137497101967</v>
       </c>
       <c r="E91">
-        <v>-22.18809824497994</v>
+        <v>-24.85414674751571</v>
       </c>
       <c r="F91">
-        <v>0.8304174648739266</v>
+        <v>1.664475751730665</v>
       </c>
       <c r="G91">
-        <v>-0.5809952717193487</v>
+        <v>-0.5774993356298783</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.420223536029156</v>
       </c>
       <c r="E92">
-        <v>-24.42779091969354</v>
+        <v>-25.32853609913723</v>
       </c>
       <c r="F92">
-        <v>1.080768318082799</v>
+        <v>1.640212870502667</v>
       </c>
       <c r="G92">
-        <v>-0.2290875914403608</v>
+        <v>-0.3093881840409227</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.571804689645749</v>
       </c>
       <c r="E93">
-        <v>-26.81480391082468</v>
+        <v>-27.27113823657762</v>
       </c>
       <c r="F93">
-        <v>0.9060175875230208</v>
+        <v>2.051778930909574</v>
       </c>
       <c r="G93">
-        <v>-0.7378720931887924</v>
+        <v>-0.8159016515494143</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.689286711011271</v>
       </c>
       <c r="E94">
-        <v>-28.53268958258245</v>
+        <v>-29.83713010591391</v>
       </c>
       <c r="F94">
-        <v>0.8232421464308773</v>
+        <v>1.582464065383903</v>
       </c>
       <c r="G94">
-        <v>-0.07892786687009828</v>
+        <v>-1.060398681806749</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.764834100028334</v>
       </c>
       <c r="E95">
-        <v>-29.79690819977779</v>
+        <v>-31.40037291878375</v>
       </c>
       <c r="F95">
-        <v>-0.1000594741990628</v>
+        <v>1.845429297402606</v>
       </c>
       <c r="G95">
-        <v>-1.26870813877431</v>
+        <v>-0.8412339460159174</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.781741603644328</v>
       </c>
       <c r="E96">
-        <v>-31.6078087276531</v>
+        <v>-33.15615965374871</v>
       </c>
       <c r="F96">
-        <v>0.1513235247936975</v>
+        <v>0.8165224300593678</v>
       </c>
       <c r="G96">
-        <v>-0.2140908201474623</v>
+        <v>-1.489908860071792</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>2.739225589535513</v>
       </c>
       <c r="E97">
-        <v>-33.77450692983707</v>
+        <v>-35.37054495147045</v>
       </c>
       <c r="F97">
-        <v>-0.08484816358145551</v>
+        <v>0.8160204394132712</v>
       </c>
       <c r="G97">
-        <v>-1.241319995527919</v>
+        <v>-1.784600381795556</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>2.615387375165041</v>
       </c>
       <c r="E98">
-        <v>-36.96882683197462</v>
+        <v>-36.15005382478078</v>
       </c>
       <c r="F98">
-        <v>-0.3971385325998552</v>
+        <v>0.9004227940845129</v>
       </c>
       <c r="G98">
-        <v>-1.594760458391589</v>
+        <v>-0.7214319240407717</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>2.425039790696862</v>
       </c>
       <c r="E99">
-        <v>-38.0952688917236</v>
+        <v>-39.72905174421091</v>
       </c>
       <c r="F99">
-        <v>-0.4748766715155747</v>
+        <v>0.737867288428749</v>
       </c>
       <c r="G99">
-        <v>-1.997888899254181</v>
+        <v>-0.6889157457540501</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>2.129924581025349</v>
       </c>
       <c r="E100">
-        <v>-40.33437965752722</v>
+        <v>-41.73464948357201</v>
       </c>
       <c r="F100">
-        <v>-0.62895218006888</v>
+        <v>-0.04023726547109094</v>
       </c>
       <c r="G100">
-        <v>-2.261179896537958</v>
+        <v>-1.17944920994448</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>1.777888484483144</v>
       </c>
       <c r="E101">
-        <v>-43.51650890763613</v>
+        <v>-44.48119840430513</v>
       </c>
       <c r="F101">
-        <v>-0.5399581848839207</v>
+        <v>0.1246351838103031</v>
       </c>
       <c r="G101">
-        <v>-1.832311964107533</v>
+        <v>-1.342914017037073</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>1.277197835869897</v>
       </c>
       <c r="E102">
-        <v>-45.14624556859759</v>
+        <v>-46.19328310085907</v>
       </c>
       <c r="F102">
-        <v>-1.522697651766934</v>
+        <v>0.2556033836625161</v>
       </c>
       <c r="G102">
-        <v>-2.468747791304722</v>
+        <v>-1.203881036024301</v>
       </c>
     </row>
   </sheetData>
